--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868517</v>
+        <v>119868779</v>
       </c>
       <c r="B2" t="n">
-        <v>57226</v>
+        <v>102833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>222009</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584670</v>
+        <v>584828</v>
       </c>
       <c r="R2" t="n">
-        <v>6341686</v>
+        <v>6341578</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868469</v>
+        <v>119868781</v>
       </c>
       <c r="B3" t="n">
-        <v>56764</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,29 +838,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584892</v>
+        <v>584763</v>
       </c>
       <c r="R3" t="n">
-        <v>6341634</v>
+        <v>6341564</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868779</v>
+        <v>119867936</v>
       </c>
       <c r="B4" t="n">
-        <v>102833</v>
+        <v>57557</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,46 +941,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222009</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584828</v>
+        <v>584581</v>
       </c>
       <c r="R4" t="n">
-        <v>6341578</v>
+        <v>6341695</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868780</v>
+        <v>119868469</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>56764</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1088,24 +1083,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584757</v>
+        <v>584892</v>
       </c>
       <c r="R5" t="n">
-        <v>6341584</v>
+        <v>6341634</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867936</v>
+        <v>119868517</v>
       </c>
       <c r="B6" t="n">
-        <v>57557</v>
+        <v>57226</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584581</v>
+        <v>584670</v>
       </c>
       <c r="R6" t="n">
-        <v>6341695</v>
+        <v>6341686</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1295,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868466</v>
+        <v>119868780</v>
       </c>
       <c r="B7" t="n">
-        <v>56764</v>
+        <v>90966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,21 +1311,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,24 +1333,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584953</v>
+        <v>584757</v>
       </c>
       <c r="R7" t="n">
-        <v>6341612</v>
+        <v>6341584</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868781</v>
+        <v>119868466</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>56764</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1458,24 +1458,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584763</v>
+        <v>584953</v>
       </c>
       <c r="R8" t="n">
-        <v>6341564</v>
+        <v>6341612</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1499,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868779</v>
+        <v>119868781</v>
       </c>
       <c r="B2" t="n">
-        <v>102833</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222009</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584828</v>
+        <v>584763</v>
       </c>
       <c r="R2" t="n">
-        <v>6341578</v>
+        <v>6341564</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868781</v>
+        <v>119868779</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>102833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,50 +812,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>222009</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584763</v>
+        <v>584828</v>
       </c>
       <c r="R3" t="n">
-        <v>6341564</v>
+        <v>6341578</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868781</v>
+        <v>119868466</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>56764</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584763</v>
+        <v>584953</v>
       </c>
       <c r="R2" t="n">
-        <v>6341564</v>
+        <v>6341612</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868779</v>
+        <v>119867936</v>
       </c>
       <c r="B3" t="n">
-        <v>102833</v>
+        <v>57557</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,46 +816,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222009</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584828</v>
+        <v>584581</v>
       </c>
       <c r="R3" t="n">
-        <v>6341578</v>
+        <v>6341695</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867936</v>
+        <v>119868780</v>
       </c>
       <c r="B4" t="n">
-        <v>57557</v>
+        <v>90966</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,19 +958,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584581</v>
+        <v>584757</v>
       </c>
       <c r="R4" t="n">
-        <v>6341695</v>
+        <v>6341584</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868469</v>
+        <v>119868781</v>
       </c>
       <c r="B5" t="n">
-        <v>56764</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,29 +1083,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584892</v>
+        <v>584763</v>
       </c>
       <c r="R5" t="n">
-        <v>6341634</v>
+        <v>6341564</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868517</v>
+        <v>119867714</v>
       </c>
       <c r="B6" t="n">
-        <v>57226</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1215,17 +1210,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584670</v>
+        <v>585045</v>
       </c>
       <c r="R6" t="n">
-        <v>6341686</v>
+        <v>6341634</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1244,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1279,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1295,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868780</v>
+        <v>119868469</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>56764</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,24 +1328,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584757</v>
+        <v>584892</v>
       </c>
       <c r="R7" t="n">
-        <v>6341584</v>
+        <v>6341634</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868466</v>
+        <v>119868517</v>
       </c>
       <c r="B8" t="n">
-        <v>56764</v>
+        <v>57226</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,20 +1432,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,24 +1458,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584953</v>
+        <v>584670</v>
       </c>
       <c r="R8" t="n">
-        <v>6341612</v>
+        <v>6341686</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119867714</v>
+        <v>119868779</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>102833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,26 +1556,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>222009</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585045</v>
+        <v>584828</v>
       </c>
       <c r="R9" t="n">
-        <v>6341634</v>
+        <v>6341578</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868466</v>
+        <v>119868780</v>
       </c>
       <c r="B2" t="n">
-        <v>56764</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584953</v>
+        <v>584757</v>
       </c>
       <c r="R2" t="n">
-        <v>6341612</v>
+        <v>6341584</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867936</v>
+        <v>119868779</v>
       </c>
       <c r="B3" t="n">
-        <v>57557</v>
+        <v>102833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +816,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>222009</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584581</v>
+        <v>584828</v>
       </c>
       <c r="R3" t="n">
-        <v>6341695</v>
+        <v>6341578</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868780</v>
+        <v>119867936</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>57557</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,24 +963,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584757</v>
+        <v>584581</v>
       </c>
       <c r="R4" t="n">
-        <v>6341584</v>
+        <v>6341695</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868781</v>
+        <v>119868517</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>57226</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1057,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,24 +1083,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584763</v>
+        <v>584670</v>
       </c>
       <c r="R5" t="n">
-        <v>6341564</v>
+        <v>6341686</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867714</v>
+        <v>119868469</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>56764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,25 +1177,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1208,19 +1203,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585045</v>
+        <v>584892</v>
       </c>
       <c r="R6" t="n">
         <v>6341634</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868469</v>
+        <v>119867714</v>
       </c>
       <c r="B7" t="n">
-        <v>56764</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,25 +1307,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1328,29 +1333,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584892</v>
+        <v>585045</v>
       </c>
       <c r="R7" t="n">
         <v>6341634</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868517</v>
+        <v>119868781</v>
       </c>
       <c r="B8" t="n">
-        <v>57226</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,25 +1427,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1458,19 +1453,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584670</v>
+        <v>584763</v>
       </c>
       <c r="R8" t="n">
-        <v>6341686</v>
+        <v>6341564</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868779</v>
+        <v>119868466</v>
       </c>
       <c r="B9" t="n">
-        <v>102833</v>
+        <v>56764</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,35 +1552,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222009</v>
+        <v>102954</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584828</v>
+        <v>584953</v>
       </c>
       <c r="R9" t="n">
-        <v>6341578</v>
+        <v>6341612</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868469</v>
+        <v>119867714</v>
       </c>
       <c r="B6" t="n">
-        <v>56764</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1177,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1203,29 +1203,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584892</v>
+        <v>585045</v>
       </c>
       <c r="R6" t="n">
         <v>6341634</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119867714</v>
+        <v>119868781</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>8421</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,25 +1297,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,19 +1323,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585045</v>
+        <v>584763</v>
       </c>
       <c r="R7" t="n">
-        <v>6341634</v>
+        <v>6341564</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1415,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868781</v>
+        <v>119868469</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>56764</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1426,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1453,24 +1448,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584763</v>
+        <v>584892</v>
       </c>
       <c r="R8" t="n">
-        <v>6341564</v>
+        <v>6341634</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867714</v>
+        <v>119868469</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>56764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1177,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1203,19 +1203,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585045</v>
+        <v>584892</v>
       </c>
       <c r="R6" t="n">
         <v>6341634</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868781</v>
+        <v>119867714</v>
       </c>
       <c r="B7" t="n">
-        <v>8421</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,25 +1307,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1323,24 +1333,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584763</v>
+        <v>585045</v>
       </c>
       <c r="R7" t="n">
-        <v>6341564</v>
+        <v>6341634</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1404,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1410,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868469</v>
+        <v>119868781</v>
       </c>
       <c r="B8" t="n">
-        <v>56764</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1448,29 +1453,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584892</v>
+        <v>584763</v>
       </c>
       <c r="R8" t="n">
-        <v>6341634</v>
+        <v>6341564</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868780</v>
+        <v>119868466</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>56774</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584757</v>
+        <v>584953</v>
       </c>
       <c r="R2" t="n">
-        <v>6341584</v>
+        <v>6341612</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868779</v>
+        <v>119868517</v>
       </c>
       <c r="B3" t="n">
-        <v>102833</v>
+        <v>57236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,46 +816,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222009</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584828</v>
+        <v>584670</v>
       </c>
       <c r="R3" t="n">
-        <v>6341578</v>
+        <v>6341686</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867936</v>
+        <v>119868780</v>
       </c>
       <c r="B4" t="n">
-        <v>57557</v>
+        <v>90984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,19 +958,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584581</v>
+        <v>584757</v>
       </c>
       <c r="R4" t="n">
-        <v>6341695</v>
+        <v>6341584</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868517</v>
+        <v>119867936</v>
       </c>
       <c r="B5" t="n">
-        <v>57226</v>
+        <v>57567</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584670</v>
+        <v>584581</v>
       </c>
       <c r="R5" t="n">
-        <v>6341686</v>
+        <v>6341695</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868469</v>
+        <v>119867714</v>
       </c>
       <c r="B6" t="n">
-        <v>56764</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1177,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1203,29 +1203,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584892</v>
+        <v>585045</v>
       </c>
       <c r="R6" t="n">
         <v>6341634</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119867714</v>
+        <v>119868469</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>56774</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,25 +1297,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,19 +1323,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585045</v>
+        <v>584892</v>
       </c>
       <c r="R7" t="n">
         <v>6341634</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868781</v>
+        <v>119868779</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>102856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,50 +1427,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>222009</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584763</v>
+        <v>584828</v>
       </c>
       <c r="R8" t="n">
-        <v>6341564</v>
+        <v>6341578</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868466</v>
+        <v>119868781</v>
       </c>
       <c r="B9" t="n">
-        <v>56764</v>
+        <v>8421</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,21 +1556,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1578,24 +1578,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584953</v>
+        <v>584763</v>
       </c>
       <c r="R9" t="n">
-        <v>6341612</v>
+        <v>6341564</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868779</v>
+        <v>119868781</v>
       </c>
       <c r="B8" t="n">
-        <v>102856</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,50 +1427,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222009</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584828</v>
+        <v>584763</v>
       </c>
       <c r="R8" t="n">
-        <v>6341578</v>
+        <v>6341564</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868781</v>
+        <v>119868779</v>
       </c>
       <c r="B9" t="n">
-        <v>8421</v>
+        <v>102856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,50 +1552,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>222009</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584763</v>
+        <v>584828</v>
       </c>
       <c r="R9" t="n">
-        <v>6341564</v>
+        <v>6341578</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868466</v>
+        <v>119867714</v>
       </c>
       <c r="B2" t="n">
-        <v>56774</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584953</v>
+        <v>585045</v>
       </c>
       <c r="R2" t="n">
-        <v>6341612</v>
+        <v>6341634</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868517</v>
+        <v>119868780</v>
       </c>
       <c r="B3" t="n">
-        <v>57236</v>
+        <v>90984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,19 +833,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584670</v>
+        <v>584757</v>
       </c>
       <c r="R3" t="n">
-        <v>6341686</v>
+        <v>6341584</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868780</v>
+        <v>119868469</v>
       </c>
       <c r="B4" t="n">
-        <v>90984</v>
+        <v>56774</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,24 +958,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584757</v>
+        <v>584892</v>
       </c>
       <c r="R4" t="n">
-        <v>6341584</v>
+        <v>6341634</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867936</v>
+        <v>119868466</v>
       </c>
       <c r="B5" t="n">
-        <v>57567</v>
+        <v>56774</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,19 +1088,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584581</v>
+        <v>584953</v>
       </c>
       <c r="R5" t="n">
-        <v>6341695</v>
+        <v>6341612</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867714</v>
+        <v>119867936</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>57567</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1205,17 +1215,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585045</v>
+        <v>584581</v>
       </c>
       <c r="R6" t="n">
-        <v>6341634</v>
+        <v>6341695</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868469</v>
+        <v>119868781</v>
       </c>
       <c r="B7" t="n">
-        <v>56774</v>
+        <v>8421</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,21 +1311,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1323,29 +1333,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584892</v>
+        <v>584763</v>
       </c>
       <c r="R7" t="n">
-        <v>6341634</v>
+        <v>6341564</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1409,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1415,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868781</v>
+        <v>119868779</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>102856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,50 +1432,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>222009</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584763</v>
+        <v>584828</v>
       </c>
       <c r="R8" t="n">
-        <v>6341564</v>
+        <v>6341578</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1545,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868779</v>
+        <v>119868517</v>
       </c>
       <c r="B9" t="n">
-        <v>102856</v>
+        <v>57236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,46 +1561,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222009</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584828</v>
+        <v>584670</v>
       </c>
       <c r="R9" t="n">
-        <v>6341578</v>
+        <v>6341686</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867714</v>
+        <v>119868517</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>57236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585045</v>
+        <v>584670</v>
       </c>
       <c r="R2" t="n">
-        <v>6341634</v>
+        <v>6341686</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868780</v>
+        <v>119868779</v>
       </c>
       <c r="B3" t="n">
-        <v>90984</v>
+        <v>102856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,50 +807,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>222009</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584757</v>
+        <v>584828</v>
       </c>
       <c r="R3" t="n">
-        <v>6341584</v>
+        <v>6341578</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868466</v>
+        <v>119867714</v>
       </c>
       <c r="B5" t="n">
-        <v>56774</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1088,21 +1088,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584953</v>
+        <v>585045</v>
       </c>
       <c r="R5" t="n">
-        <v>6341612</v>
+        <v>6341634</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1129,22 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867936</v>
+        <v>119868466</v>
       </c>
       <c r="B6" t="n">
-        <v>57567</v>
+        <v>56774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1182,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,19 +1208,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584581</v>
+        <v>584953</v>
       </c>
       <c r="R6" t="n">
-        <v>6341695</v>
+        <v>6341612</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1295,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868781</v>
+        <v>119867936</v>
       </c>
       <c r="B7" t="n">
-        <v>8421</v>
+        <v>57567</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,24 +1333,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584763</v>
+        <v>584581</v>
       </c>
       <c r="R7" t="n">
-        <v>6341564</v>
+        <v>6341695</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1404,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1420,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868779</v>
+        <v>119868780</v>
       </c>
       <c r="B8" t="n">
-        <v>102856</v>
+        <v>90984</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,50 +1427,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222009</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584828</v>
+        <v>584757</v>
       </c>
       <c r="R8" t="n">
-        <v>6341578</v>
+        <v>6341584</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868517</v>
+        <v>119868781</v>
       </c>
       <c r="B9" t="n">
-        <v>57236</v>
+        <v>8421</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,25 +1552,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1583,19 +1578,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584670</v>
+        <v>584763</v>
       </c>
       <c r="R9" t="n">
-        <v>6341686</v>
+        <v>6341564</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868517</v>
+        <v>119868469</v>
       </c>
       <c r="B2" t="n">
-        <v>57236</v>
+        <v>56774</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,19 +713,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584670</v>
+        <v>584892</v>
       </c>
       <c r="R2" t="n">
-        <v>6341686</v>
+        <v>6341634</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868779</v>
+        <v>119867714</v>
       </c>
       <c r="B3" t="n">
-        <v>102856</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +821,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222009</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584828</v>
+        <v>585045</v>
       </c>
       <c r="R3" t="n">
-        <v>6341578</v>
+        <v>6341634</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868469</v>
+        <v>119867936</v>
       </c>
       <c r="B4" t="n">
-        <v>56774</v>
+        <v>57567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,29 +963,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584892</v>
+        <v>584581</v>
       </c>
       <c r="R4" t="n">
-        <v>6341634</v>
+        <v>6341695</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867714</v>
+        <v>119868781</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1057,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1088,19 +1083,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585045</v>
+        <v>584763</v>
       </c>
       <c r="R5" t="n">
-        <v>6341634</v>
+        <v>6341564</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1295,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119867936</v>
+        <v>119868780</v>
       </c>
       <c r="B7" t="n">
-        <v>57567</v>
+        <v>90984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,19 +1333,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584581</v>
+        <v>584757</v>
       </c>
       <c r="R7" t="n">
-        <v>6341695</v>
+        <v>6341584</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1409,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1415,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868780</v>
+        <v>119868779</v>
       </c>
       <c r="B8" t="n">
-        <v>90984</v>
+        <v>102856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,50 +1432,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>222009</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584757</v>
+        <v>584828</v>
       </c>
       <c r="R8" t="n">
-        <v>6341584</v>
+        <v>6341578</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1545,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868781</v>
+        <v>119868517</v>
       </c>
       <c r="B9" t="n">
-        <v>8421</v>
+        <v>57236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,25 +1557,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1578,24 +1583,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584763</v>
+        <v>584670</v>
       </c>
       <c r="R9" t="n">
-        <v>6341564</v>
+        <v>6341686</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 15512-2022 artfynd.xlsx
+++ b/artfynd/A 15512-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868469</v>
+        <v>119867714</v>
       </c>
       <c r="B2" t="n">
-        <v>56774</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,29 +713,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584892</v>
+        <v>585045</v>
       </c>
       <c r="R2" t="n">
         <v>6341634</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867714</v>
+        <v>119868517</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>57236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,17 +835,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585045</v>
+        <v>584670</v>
       </c>
       <c r="R3" t="n">
-        <v>6341634</v>
+        <v>6341686</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867936</v>
+        <v>119868780</v>
       </c>
       <c r="B4" t="n">
-        <v>57567</v>
+        <v>90984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,19 +953,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584581</v>
+        <v>584757</v>
       </c>
       <c r="R4" t="n">
-        <v>6341695</v>
+        <v>6341584</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868781</v>
+        <v>119868469</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>56774</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,24 +1078,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584763</v>
+        <v>584892</v>
       </c>
       <c r="R5" t="n">
-        <v>6341564</v>
+        <v>6341634</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868466</v>
+        <v>119868781</v>
       </c>
       <c r="B6" t="n">
-        <v>56774</v>
+        <v>8421</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1208,24 +1208,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584953</v>
+        <v>584763</v>
       </c>
       <c r="R6" t="n">
-        <v>6341612</v>
+        <v>6341564</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1295,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868780</v>
+        <v>119868779</v>
       </c>
       <c r="B7" t="n">
-        <v>90984</v>
+        <v>102856</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,50 +1307,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>222009</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584757</v>
+        <v>584828</v>
       </c>
       <c r="R7" t="n">
-        <v>6341584</v>
+        <v>6341578</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868779</v>
+        <v>119867936</v>
       </c>
       <c r="B8" t="n">
-        <v>102856</v>
+        <v>57567</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,46 +1436,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222009</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söberg, Sm</t>
+          <t>Stensberg, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584828</v>
+        <v>584581</v>
       </c>
       <c r="R8" t="n">
-        <v>6341578</v>
+        <v>6341695</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868517</v>
+        <v>119868466</v>
       </c>
       <c r="B9" t="n">
-        <v>57236</v>
+        <v>56774</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,20 +1552,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>102954</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1583,19 +1578,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stensberg, Sm</t>
+          <t>Söberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584670</v>
+        <v>584953</v>
       </c>
       <c r="R9" t="n">
-        <v>6341686</v>
+        <v>6341612</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
